--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,25 +60,25 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:31:00+00:00</t>
+    <t>2026-08-31T16:07:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Medizininformatik-Initiative</t>
+    <t>NUM-DIZ</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Medizininformatik-Initiative (https://www.medizininformatik-initiative.de)</t>
+    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t/>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
   <si>
     <t>Value Set (all codes)</t>
@@ -436,52 +439,54 @@
       <c r="A15" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -496,111 +501,111 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2"/>
     </row>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-sdd-einkommen.xlsx
+++ b/CodeSystem-mii-cs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
